--- a/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T09:53:32+00:00</t>
+    <t>2026-07-15T08:23:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T08:23:09+00:00</t>
+    <t>2026-07-15T12:56:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:56:21+00:00</t>
+    <t>2026-07-15T14:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:31:09+00:00</t>
+    <t>2026-07-16T16:04:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T16:04:02+00:00</t>
+    <t>2026-07-17T10:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T10:31:48+00:00</t>
+    <t>2026-07-17T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:58:48+00:00</t>
+    <t>2026-07-20T08:24:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUILLET-2026/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T08:24:23+00:00</t>
+    <t>2026-07-20T09:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
